--- a/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-simplified-publish.xlsx
+++ b/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-simplified-publish.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AQ$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AQ$88</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2607" uniqueCount="532">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3469" uniqueCount="613">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:19:16+00:00</t>
+    <t>2026-08-06T13:23:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1192,6 +1192,214 @@
     <t>http://terminology.hl7.org/ValueSet/v3-ConfidentialityClassification</t>
   </si>
   <si>
+    <t>DocumentReference.securityLabel:confidentiality.id</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel.id</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel:confidentiality.extension</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel.extension</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel:confidentiality.coding</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel.coding</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel:confidentiality.coding.id</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel.coding.id</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel:confidentiality.coding.extension</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel.coding.extension</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel:confidentiality.coding.system</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/CodeSystem/v3-Confidentiality</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel:confidentiality.coding.version</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel.coding.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel:confidentiality.coding.code</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel.coding.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel:confidentiality.coding.display</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel.coding.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel:confidentiality.coding.userSelected</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel.coding.userSelected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel:confidentiality.text</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
     <t>DocumentReference.securityLabel:visibilityStatus</t>
   </si>
   <si>
@@ -1202,6 +1410,42 @@
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J110-StatutVisibiliteDocument-CISIS/FHIR/JDV-J110-StatutVisibiliteDocument-CISIS</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel:visibilityStatus.id</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel:visibilityStatus.extension</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel:visibilityStatus.coding</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel:visibilityStatus.coding.id</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel:visibilityStatus.coding.extension</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel:visibilityStatus.coding.system</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_A07-StatutVisibiliteDocument/FHIR/TRE-A07-StatutVisibiliteDocument</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel:visibilityStatus.coding.version</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel:visibilityStatus.coding.code</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel:visibilityStatus.coding.display</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel:visibilityStatus.coding.userSelected</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel:visibilityStatus.text</t>
   </si>
   <si>
     <t>DocumentReference.content</t>
@@ -2006,11 +2250,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AQ66"/>
+  <dimension ref="A1:AQ88"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="43.578125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="43.578125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="56.58203125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="44.56640625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.37890625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -6727,16 +6971,14 @@
         <v>369</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
         <v>374</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="C39" t="s" s="2">
         <v>375</v>
       </c>
+      <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>80</v>
       </c>
@@ -6745,32 +6987,28 @@
         <v>81</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>242</v>
+        <v>107</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>376</v>
+        <v>108</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>362</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>80</v>
       </c>
@@ -6794,101 +7032,105 @@
         <v>80</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="Y39" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="Z39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF39" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AN39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ39" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="40" hidden="true">
+      <c r="A40" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="B40" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="AA39" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB39" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC39" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD39" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE39" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF39" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="AG39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI39" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ39" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK39" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL39" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="AO39" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP39" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="AQ39" t="s" s="2">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="B40" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>316</v>
+        <v>114</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>379</v>
+        <v>115</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>80</v>
@@ -6925,22 +7167,22 @@
         <v>80</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>378</v>
+        <v>121</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>82</v>
@@ -6949,16 +7191,16 @@
         <v>80</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>381</v>
+        <v>80</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>382</v>
+        <v>111</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>80</v>
@@ -6975,10 +7217,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6989,7 +7231,7 @@
         <v>81</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>80</v>
@@ -6998,19 +7240,23 @@
         <v>80</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>107</v>
+        <v>147</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>108</v>
+        <v>380</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
+        <v>381</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>383</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>80</v>
       </c>
@@ -7058,19 +7304,19 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>110</v>
+        <v>384</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>80</v>
@@ -7079,7 +7325,7 @@
         <v>80</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>111</v>
+        <v>385</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>80</v>
@@ -7088,7 +7334,7 @@
         <v>80</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>80</v>
+        <v>386</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>80</v>
@@ -7096,21 +7342,21 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>80</v>
@@ -7122,17 +7368,15 @@
         <v>80</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>80</v>
@@ -7181,19 +7425,19 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>122</v>
+        <v>80</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>80</v>
@@ -7219,14 +7463,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>327</v>
+        <v>113</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7239,26 +7483,24 @@
         <v>80</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K43" t="s" s="2">
         <v>114</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>328</v>
+        <v>115</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>329</v>
+        <v>116</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="O43" t="s" s="2">
-        <v>330</v>
-      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>80</v>
       </c>
@@ -7294,19 +7536,19 @@
         <v>80</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>331</v>
+        <v>121</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7327,7 +7569,7 @@
         <v>80</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>192</v>
+        <v>111</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>80</v>
@@ -7344,10 +7586,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7370,16 +7612,20 @@
         <v>94</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>387</v>
+        <v>135</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+        <v>394</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>396</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>80</v>
       </c>
@@ -7388,7 +7634,7 @@
         <v>80</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>80</v>
+        <v>397</v>
       </c>
       <c r="T44" t="s" s="2">
         <v>80</v>
@@ -7427,10 +7673,10 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>93</v>
@@ -7445,30 +7691,30 @@
         <v>80</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>390</v>
+        <v>80</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>382</v>
+        <v>399</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>391</v>
+        <v>80</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>393</v>
+        <v>80</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7488,18 +7734,20 @@
         <v>80</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K45" t="s" s="2">
         <v>107</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>108</v>
+        <v>403</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>404</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>405</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>80</v>
@@ -7548,7 +7796,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>110</v>
+        <v>406</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7560,7 +7808,7 @@
         <v>80</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>80</v>
@@ -7569,7 +7817,7 @@
         <v>80</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>111</v>
+        <v>407</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>80</v>
@@ -7578,7 +7826,7 @@
         <v>80</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>80</v>
+        <v>408</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>80</v>
@@ -7586,21 +7834,21 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>395</v>
+        <v>409</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>395</v>
+        <v>410</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>80</v>
@@ -7609,21 +7857,21 @@
         <v>80</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>114</v>
+        <v>169</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>115</v>
+        <v>411</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O46" s="2"/>
+        <v>412</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" t="s" s="2">
+        <v>413</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>80</v>
       </c>
@@ -7659,31 +7907,31 @@
         <v>80</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>121</v>
+        <v>414</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>80</v>
@@ -7692,7 +7940,7 @@
         <v>80</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>111</v>
+        <v>250</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>80</v>
@@ -7701,7 +7949,7 @@
         <v>80</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>80</v>
+        <v>415</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>80</v>
@@ -7709,10 +7957,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>396</v>
+        <v>417</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7720,7 +7968,7 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>93</v>
@@ -7735,17 +7983,17 @@
         <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>169</v>
+        <v>107</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>397</v>
+        <v>418</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>398</v>
+        <v>419</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>399</v>
+        <v>420</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>80</v>
@@ -7758,7 +8006,7 @@
         <v>80</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>400</v>
+        <v>80</v>
       </c>
       <c r="U47" t="s" s="2">
         <v>80</v>
@@ -7770,13 +8018,13 @@
         <v>80</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>224</v>
+        <v>80</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>401</v>
+        <v>80</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>402</v>
+        <v>80</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>80</v>
@@ -7794,7 +8042,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>403</v>
+        <v>421</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7815,7 +8063,7 @@
         <v>80</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>404</v>
+        <v>422</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>80</v>
@@ -7824,18 +8072,18 @@
         <v>80</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>405</v>
+        <v>423</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>406</v>
+        <v>424</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>406</v>
+        <v>425</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7849,7 +8097,7 @@
         <v>93</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>80</v>
@@ -7858,17 +8106,19 @@
         <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>169</v>
+        <v>426</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>407</v>
+        <v>427</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>428</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>429</v>
+      </c>
       <c r="O48" t="s" s="2">
-        <v>409</v>
+        <v>430</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>80</v>
@@ -7881,7 +8131,7 @@
         <v>80</v>
       </c>
       <c r="T48" t="s" s="2">
-        <v>410</v>
+        <v>80</v>
       </c>
       <c r="U48" t="s" s="2">
         <v>80</v>
@@ -7893,13 +8143,13 @@
         <v>80</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>173</v>
+        <v>80</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>174</v>
+        <v>80</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>175</v>
+        <v>80</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>80</v>
@@ -7917,7 +8167,7 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>411</v>
+        <v>431</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7938,7 +8188,7 @@
         <v>80</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>412</v>
+        <v>432</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>80</v>
@@ -7947,7 +8197,7 @@
         <v>80</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>80</v>
+        <v>433</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>80</v>
@@ -7955,10 +8205,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>413</v>
+        <v>434</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>413</v>
+        <v>435</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7966,7 +8216,7 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>93</v>
@@ -7978,22 +8228,22 @@
         <v>80</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>414</v>
+        <v>107</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>415</v>
+        <v>436</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>416</v>
+        <v>437</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>417</v>
+        <v>438</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>418</v>
+        <v>439</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>80</v>
@@ -8042,7 +8292,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>419</v>
+        <v>440</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8063,7 +8313,7 @@
         <v>80</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>420</v>
+        <v>441</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>80</v>
@@ -8072,20 +8322,22 @@
         <v>80</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>421</v>
+        <v>442</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
-        <v>422</v>
+        <v>443</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="C50" s="2"/>
+        <v>358</v>
+      </c>
+      <c r="C50" t="s" s="2">
+        <v>444</v>
+      </c>
       <c r="D50" t="s" s="2">
         <v>80</v>
       </c>
@@ -8094,10 +8346,10 @@
         <v>81</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>80</v>
@@ -8106,19 +8358,19 @@
         <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>423</v>
+        <v>242</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>424</v>
+        <v>445</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>425</v>
+        <v>360</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>426</v>
+        <v>361</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>427</v>
+        <v>362</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>80</v>
@@ -8131,7 +8383,7 @@
         <v>80</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>428</v>
+        <v>80</v>
       </c>
       <c r="U50" t="s" s="2">
         <v>80</v>
@@ -8143,13 +8395,11 @@
         <v>80</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="Y50" s="2"/>
       <c r="Z50" t="s" s="2">
-        <v>80</v>
+        <v>446</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>80</v>
@@ -8167,13 +8417,13 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>429</v>
+        <v>358</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>80</v>
@@ -8185,30 +8435,30 @@
         <v>80</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>80</v>
+        <v>365</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>430</v>
+        <v>366</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>80</v>
+        <v>367</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>431</v>
+        <v>368</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>80</v>
+        <v>369</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>432</v>
+        <v>447</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>432</v>
+        <v>375</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8228,23 +8478,19 @@
         <v>80</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>433</v>
+        <v>107</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>434</v>
+        <v>108</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>437</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>80</v>
       </c>
@@ -8292,7 +8538,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>438</v>
+        <v>110</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8304,7 +8550,7 @@
         <v>80</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>80</v>
@@ -8313,7 +8559,7 @@
         <v>80</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>439</v>
+        <v>111</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>80</v>
@@ -8330,21 +8576,21 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>440</v>
+        <v>377</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>80</v>
@@ -8353,23 +8599,21 @@
         <v>80</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>414</v>
+        <v>114</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>441</v>
+        <v>115</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>442</v>
+        <v>116</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>444</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>80</v>
       </c>
@@ -8405,31 +8649,31 @@
         <v>80</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>445</v>
+        <v>121</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>80</v>
@@ -8438,7 +8682,7 @@
         <v>80</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>446</v>
+        <v>111</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>80</v>
@@ -8455,10 +8699,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>447</v>
+        <v>379</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8466,10 +8710,10 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>80</v>
@@ -8481,17 +8725,19 @@
         <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>107</v>
+        <v>147</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>448</v>
+        <v>380</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>381</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>382</v>
+      </c>
       <c r="O53" t="s" s="2">
-        <v>450</v>
+        <v>383</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>80</v>
@@ -8504,7 +8750,7 @@
         <v>80</v>
       </c>
       <c r="T53" t="s" s="2">
-        <v>451</v>
+        <v>80</v>
       </c>
       <c r="U53" t="s" s="2">
         <v>80</v>
@@ -8540,13 +8786,13 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>452</v>
+        <v>384</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>80</v>
@@ -8561,7 +8807,7 @@
         <v>80</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>453</v>
+        <v>385</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>80</v>
@@ -8570,18 +8816,18 @@
         <v>80</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>80</v>
+        <v>386</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>454</v>
+        <v>388</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8595,27 +8841,25 @@
         <v>93</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>455</v>
+        <v>107</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>456</v>
+        <v>108</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>457</v>
+        <v>109</v>
       </c>
       <c r="N54" s="2"/>
-      <c r="O54" t="s" s="2">
-        <v>458</v>
-      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>80</v>
       </c>
@@ -8663,7 +8907,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>459</v>
+        <v>110</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8675,7 +8919,7 @@
         <v>80</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>80</v>
@@ -8684,7 +8928,7 @@
         <v>80</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>439</v>
+        <v>111</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>80</v>
@@ -8699,44 +8943,44 @@
         <v>80</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>460</v>
+        <v>390</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>147</v>
+        <v>114</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>461</v>
+        <v>115</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>462</v>
+        <v>116</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>463</v>
+        <v>117</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8762,53 +9006,55 @@
         <v>80</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="Y55" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="Z55" t="s" s="2">
-        <v>464</v>
+        <v>80</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AD55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>460</v>
+        <v>121</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>465</v>
+        <v>122</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>466</v>
+        <v>80</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>382</v>
+        <v>111</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>467</v>
+        <v>80</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>80</v>
@@ -8817,15 +9063,15 @@
         <v>80</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>468</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>469</v>
+        <v>452</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>469</v>
+        <v>392</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8833,13 +9079,13 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>80</v>
@@ -8848,18 +9094,20 @@
         <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>316</v>
+        <v>135</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>470</v>
+        <v>393</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>471</v>
+        <v>394</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="O56" s="2"/>
+        <v>395</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>396</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>80</v>
       </c>
@@ -8868,7 +9116,7 @@
         <v>80</v>
       </c>
       <c r="S56" t="s" s="2">
-        <v>80</v>
+        <v>453</v>
       </c>
       <c r="T56" t="s" s="2">
         <v>80</v>
@@ -8907,7 +9155,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>469</v>
+        <v>398</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8928,7 +9176,7 @@
         <v>80</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>473</v>
+        <v>399</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>80</v>
@@ -8937,7 +9185,7 @@
         <v>80</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>80</v>
+        <v>400</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>80</v>
@@ -8945,10 +9193,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>474</v>
+        <v>454</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>474</v>
+        <v>402</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8968,18 +9216,20 @@
         <v>80</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
         <v>107</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>108</v>
+        <v>403</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N57" s="2"/>
+        <v>404</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>405</v>
+      </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>80</v>
@@ -9028,7 +9278,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>110</v>
+        <v>406</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9040,7 +9290,7 @@
         <v>80</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>80</v>
@@ -9049,7 +9299,7 @@
         <v>80</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>111</v>
+        <v>407</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>80</v>
@@ -9058,7 +9308,7 @@
         <v>80</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>80</v>
+        <v>408</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>80</v>
@@ -9066,21 +9316,21 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>475</v>
+        <v>455</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>475</v>
+        <v>410</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>80</v>
@@ -9089,21 +9339,21 @@
         <v>80</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>114</v>
+        <v>169</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>115</v>
+        <v>411</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O58" s="2"/>
+        <v>412</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" t="s" s="2">
+        <v>413</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>80</v>
       </c>
@@ -9151,19 +9401,19 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>121</v>
+        <v>414</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>80</v>
@@ -9172,7 +9422,7 @@
         <v>80</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>111</v>
+        <v>250</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>80</v>
@@ -9181,7 +9431,7 @@
         <v>80</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>80</v>
+        <v>415</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>80</v>
@@ -9189,45 +9439,43 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>476</v>
+        <v>456</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>476</v>
+        <v>417</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>327</v>
+        <v>80</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="J59" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>328</v>
+        <v>418</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>419</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>330</v>
+        <v>420</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>80</v>
@@ -9276,19 +9524,19 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>331</v>
+        <v>421</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>80</v>
@@ -9297,7 +9545,7 @@
         <v>80</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>192</v>
+        <v>422</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>80</v>
@@ -9306,7 +9554,7 @@
         <v>80</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>80</v>
+        <v>423</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>80</v>
@@ -9314,10 +9562,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>477</v>
+        <v>457</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>477</v>
+        <v>425</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9328,7 +9576,7 @@
         <v>81</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>80</v>
@@ -9337,19 +9585,23 @@
         <v>80</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>478</v>
+        <v>426</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>479</v>
+        <v>427</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="N60" s="2"/>
-      <c r="O60" s="2"/>
+        <v>428</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>430</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>80</v>
       </c>
@@ -9397,13 +9649,13 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>477</v>
+        <v>431</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>80</v>
@@ -9412,22 +9664,22 @@
         <v>105</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>481</v>
+        <v>80</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>482</v>
+        <v>80</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>483</v>
+        <v>432</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>484</v>
+        <v>80</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>80</v>
+        <v>433</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>80</v>
@@ -9435,10 +9687,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>485</v>
+        <v>458</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>485</v>
+        <v>435</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9458,21 +9710,23 @@
         <v>80</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>242</v>
+        <v>107</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>486</v>
+        <v>436</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>487</v>
+        <v>437</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="O61" s="2"/>
+        <v>438</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>439</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>80</v>
       </c>
@@ -9496,13 +9750,13 @@
         <v>80</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>159</v>
+        <v>80</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>489</v>
+        <v>80</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>490</v>
+        <v>80</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>80</v>
@@ -9520,28 +9774,28 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>485</v>
+        <v>440</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>491</v>
+        <v>105</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>492</v>
+        <v>80</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>493</v>
+        <v>441</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>80</v>
@@ -9550,18 +9804,18 @@
         <v>80</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>80</v>
+        <v>442</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>494</v>
+        <v>80</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>495</v>
+        <v>459</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>495</v>
+        <v>459</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9569,7 +9823,7 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G62" t="s" s="2">
         <v>93</v>
@@ -9584,13 +9838,13 @@
         <v>94</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>496</v>
+        <v>316</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>497</v>
+        <v>460</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>498</v>
+        <v>461</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9641,13 +9895,13 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>495</v>
+        <v>459</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>80</v>
@@ -9659,13 +9913,13 @@
         <v>80</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>499</v>
+        <v>462</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>500</v>
+        <v>463</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>501</v>
+        <v>80</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>80</v>
@@ -9674,15 +9928,15 @@
         <v>80</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>502</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>503</v>
+        <v>464</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>503</v>
+        <v>464</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9696,7 +9950,7 @@
         <v>93</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>80</v>
@@ -9705,13 +9959,13 @@
         <v>80</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>242</v>
+        <v>107</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>504</v>
+        <v>108</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>505</v>
+        <v>109</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9738,11 +9992,13 @@
         <v>80</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="Y63" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="Z63" t="s" s="2">
-        <v>506</v>
+        <v>80</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>80</v>
@@ -9760,7 +10016,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>503</v>
+        <v>110</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9772,19 +10028,19 @@
         <v>80</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>507</v>
+        <v>80</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>508</v>
+        <v>80</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>509</v>
+        <v>111</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>510</v>
+        <v>80</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>80</v>
@@ -9793,29 +10049,29 @@
         <v>80</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>511</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>512</v>
+        <v>465</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>512</v>
+        <v>465</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>80</v>
@@ -9824,20 +10080,18 @@
         <v>80</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>242</v>
+        <v>114</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>513</v>
+        <v>115</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>514</v>
+        <v>116</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>516</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>80</v>
       </c>
@@ -9861,11 +10115,13 @@
         <v>80</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="Y64" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="Z64" t="s" s="2">
-        <v>517</v>
+        <v>80</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>80</v>
@@ -9883,31 +10139,31 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>512</v>
+        <v>121</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>507</v>
+        <v>122</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>508</v>
+        <v>80</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>509</v>
+        <v>111</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>508</v>
+        <v>80</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>80</v>
@@ -9916,47 +10172,51 @@
         <v>80</v>
       </c>
       <c r="AQ64" t="s" s="2">
-        <v>518</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>519</v>
+        <v>466</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>519</v>
+        <v>466</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>80</v>
+        <v>327</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I65" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="I65" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="J65" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>267</v>
+        <v>114</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>520</v>
+        <v>328</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="N65" s="2"/>
-      <c r="O65" s="2"/>
+        <v>329</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>330</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>80</v>
       </c>
@@ -10004,31 +10264,31 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>519</v>
+        <v>331</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>271</v>
+        <v>80</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>272</v>
+        <v>192</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>273</v>
+        <v>80</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>80</v>
@@ -10037,15 +10297,15 @@
         <v>80</v>
       </c>
       <c r="AQ65" t="s" s="2">
-        <v>522</v>
+        <v>80</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>523</v>
+        <v>467</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>523</v>
+        <v>467</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10053,10 +10313,10 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>80</v>
@@ -10065,20 +10325,18 @@
         <v>80</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>524</v>
+        <v>468</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>525</v>
+        <v>469</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>527</v>
-      </c>
+        <v>470</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>80</v>
@@ -10127,13 +10385,13 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>523</v>
+        <v>467</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>80</v>
@@ -10145,26 +10403,2726 @@
         <v>80</v>
       </c>
       <c r="AL66" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP66" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AQ66" t="s" s="2">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="67" hidden="true">
+      <c r="A67" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
+      <c r="P67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ67" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O68" s="2"/>
+      <c r="P68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ68" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="P69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP69" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AQ69" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="P70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ70" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="P71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP71" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="AQ71" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="P72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP72" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="AQ72" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="73" hidden="true">
+      <c r="A73" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="P73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ73" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="74" hidden="true">
+      <c r="A74" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="P74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ74" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="75" hidden="true">
+      <c r="A75" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="AM66" t="s" s="2">
+      <c r="B75" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L75" t="s" s="2">
         <v>529</v>
       </c>
-      <c r="AN66" t="s" s="2">
+      <c r="M75" t="s" s="2">
         <v>530</v>
       </c>
-      <c r="AO66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ66" t="s" s="2">
+      <c r="N75" s="2"/>
+      <c r="O75" t="s" s="2">
         <v>531</v>
+      </c>
+      <c r="P75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ75" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="N76" s="2"/>
+      <c r="O76" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="P76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ76" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="O77" s="2"/>
+      <c r="P77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="Y77" s="2"/>
+      <c r="Z77" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="AO77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ77" t="s" s="2">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="O78" s="2"/>
+      <c r="P78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ78" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="79" hidden="true">
+      <c r="A79" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="N79" s="2"/>
+      <c r="O79" s="2"/>
+      <c r="P79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AN79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ79" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="80" hidden="true">
+      <c r="A80" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O80" s="2"/>
+      <c r="P80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q80" s="2"/>
+      <c r="R80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AN80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ80" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="81" hidden="true">
+      <c r="A81" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="C81" s="2"/>
+      <c r="D81" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="E81" s="2"/>
+      <c r="F81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="J81" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K81" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O81" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="P81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q81" s="2"/>
+      <c r="R81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF81" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AN81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ81" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="82" hidden="true">
+      <c r="A82" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="C82" s="2"/>
+      <c r="D82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E82" s="2"/>
+      <c r="F82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K82" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="N82" s="2"/>
+      <c r="O82" s="2"/>
+      <c r="P82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q82" s="2"/>
+      <c r="R82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO82" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="AP82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ82" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="83" hidden="true">
+      <c r="A83" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="C83" s="2"/>
+      <c r="D83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E83" s="2"/>
+      <c r="F83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G83" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K83" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="O83" s="2"/>
+      <c r="P83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q83" s="2"/>
+      <c r="R83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF83" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="AG83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ83" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="AK83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="AN83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ83" t="s" s="2">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="C84" s="2"/>
+      <c r="D84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E84" s="2"/>
+      <c r="F84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G84" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H84" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="I84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J84" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K84" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="N84" s="2"/>
+      <c r="O84" s="2"/>
+      <c r="P84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q84" s="2"/>
+      <c r="R84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF84" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="AO84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ84" t="s" s="2">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="N85" s="2"/>
+      <c r="O85" s="2"/>
+      <c r="P85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q85" s="2"/>
+      <c r="R85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="Y85" s="2"/>
+      <c r="Z85" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="AN85" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="AO85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ85" t="s" s="2">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="O86" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="P86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q86" s="2"/>
+      <c r="R86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="Y86" s="2"/>
+      <c r="Z86" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="AN86" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="AO86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ86" t="s" s="2">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E87" s="2"/>
+      <c r="F87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K87" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="N87" s="2"/>
+      <c r="O87" s="2"/>
+      <c r="P87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q87" s="2"/>
+      <c r="R87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF87" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ87" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AN87" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="AO87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ87" t="s" s="2">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="88" hidden="true">
+      <c r="A88" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="C88" s="2"/>
+      <c r="D88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E88" s="2"/>
+      <c r="F88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K88" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="O88" s="2"/>
+      <c r="P88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q88" s="2"/>
+      <c r="R88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF88" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="AN88" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="AO88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ88" t="s" s="2">
+        <v>612</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AQ66">
+  <autoFilter ref="A1:AQ88">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10174,7 +13132,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI65">
+  <conditionalFormatting sqref="A2:AI87">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-simplified-publish.xlsx
+++ b/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-simplified-publish.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AQ$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AQ$66</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3469" uniqueCount="613">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2607" uniqueCount="534">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:23:45+00:00</t>
+    <t>2026-08-06T13:28:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1158,11 +1158,11 @@
     <t>Use of the Health Care Privacy/Security Classification (HCS) system of security-tag use is recommended.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:coding.system}
+    <t xml:space="preserve">pattern:$this}
 </t>
   </si>
   <si>
-    <t>Slice sur securityLabel.coding.system pour distinguer le niveau de confidentialité (NRV) du statut de visibilité complémentaire (TRE A07)</t>
+    <t>Slice sur securityLabel (pattern sur coding.system) pour distinguer le niveau de confidentialité (NRV) du statut de visibilité complémentaire (TRE A07)</t>
   </si>
   <si>
     <t>Composition.confidentiality, Composition.meta.security</t>
@@ -1189,217 +1189,16 @@
     <t>Niveau de confidentialité standard du document (Normal, Restreint, Très restreint).</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://terminology.hl7.org/CodeSystem/v3-Confidentiality"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>http://terminology.hl7.org/ValueSet/v3-ConfidentialityClassification</t>
   </si>
   <si>
-    <t>DocumentReference.securityLabel:confidentiality.id</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel.id</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel:confidentiality.extension</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel.extension</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel:confidentiality.coding</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel.coding</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel:confidentiality.coding.id</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel.coding.id</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel:confidentiality.coding.extension</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel.coding.extension</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel:confidentiality.coding.system</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/CodeSystem/v3-Confidentiality</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel:confidentiality.coding.version</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel.coding.version</t>
-  </si>
-  <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel:confidentiality.coding.code</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel.coding.code</t>
-  </si>
-  <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>C*E.1</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel:confidentiality.coding.display</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel.coding.display</t>
-  </si>
-  <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>C*E.2 - but note this is not well followed</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel:confidentiality.coding.userSelected</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel.coding.userSelected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
-    <t>Sometimes implied by being first</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel:confidentiality.text</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel.text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
     <t>DocumentReference.securityLabel:visibilityStatus</t>
   </si>
   <si>
@@ -1409,43 +1208,14 @@
     <t>Statut de visibilité complémentaire du document (motifs de masquage patient, représentants légaux, professionnels).</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="https://mos.esante.gouv.fr/NOS/TRE_A07-StatutVisibiliteDocument/FHIR/TRE-A07-StatutVisibiliteDocument"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J110-StatutVisibiliteDocument-CISIS/FHIR/JDV-J110-StatutVisibiliteDocument-CISIS</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel:visibilityStatus.id</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel:visibilityStatus.extension</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel:visibilityStatus.coding</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel:visibilityStatus.coding.id</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel:visibilityStatus.coding.extension</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel:visibilityStatus.coding.system</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_A07-StatutVisibiliteDocument/FHIR/TRE-A07-StatutVisibiliteDocument</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel:visibilityStatus.coding.version</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel:visibilityStatus.coding.code</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel:visibilityStatus.coding.display</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel:visibilityStatus.coding.userSelected</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel:visibilityStatus.text</t>
   </si>
   <si>
     <t>DocumentReference.content</t>
@@ -2250,11 +2020,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AQ88"/>
+  <dimension ref="A1:AQ66"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="56.58203125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="44.56640625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="43.578125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="43.578125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.37890625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -2281,7 +2051,7 @@
     <col min="26" max="26" width="102.93359375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="108.81640625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="119.3046875" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="37.78125" customWidth="true" bestFit="true" hidden="true"/>
@@ -6898,7 +6668,7 @@
         <v>80</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>80</v>
+        <v>373</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>80</v>
@@ -6917,7 +6687,7 @@
       </c>
       <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>80</v>
@@ -6971,14 +6741,16 @@
         <v>369</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="C39" s="2"/>
+        <v>358</v>
+      </c>
+      <c r="C39" t="s" s="2">
+        <v>376</v>
+      </c>
       <c r="D39" t="s" s="2">
         <v>80</v>
       </c>
@@ -6987,28 +6759,32 @@
         <v>81</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>107</v>
+        <v>242</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>108</v>
+        <v>377</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+        <v>360</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>362</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>80</v>
       </c>
@@ -7017,7 +6793,7 @@
         <v>80</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>80</v>
+        <v>378</v>
       </c>
       <c r="T39" t="s" s="2">
         <v>80</v>
@@ -7032,13 +6808,11 @@
         <v>80</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y39" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="Y39" s="2"/>
       <c r="Z39" t="s" s="2">
-        <v>80</v>
+        <v>379</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>80</v>
@@ -7056,81 +6830,79 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>110</v>
+        <v>358</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>80</v>
+        <v>365</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>111</v>
+        <v>366</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>80</v>
+        <v>367</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>80</v>
+        <v>368</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>80</v>
+        <v>369</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>114</v>
+        <v>316</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>115</v>
+        <v>381</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>382</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>80</v>
@@ -7167,22 +6939,22 @@
         <v>80</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>121</v>
+        <v>380</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>82</v>
@@ -7191,16 +6963,16 @@
         <v>80</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>80</v>
+        <v>383</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>111</v>
+        <v>384</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>80</v>
@@ -7217,10 +6989,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7231,7 +7003,7 @@
         <v>81</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>80</v>
@@ -7240,23 +7012,19 @@
         <v>80</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>147</v>
+        <v>107</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>380</v>
+        <v>108</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>383</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>80</v>
       </c>
@@ -7304,19 +7072,19 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>384</v>
+        <v>110</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>80</v>
@@ -7325,7 +7093,7 @@
         <v>80</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>385</v>
+        <v>111</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>80</v>
@@ -7334,7 +7102,7 @@
         <v>80</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>386</v>
+        <v>80</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>80</v>
@@ -7342,21 +7110,21 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>80</v>
@@ -7368,15 +7136,17 @@
         <v>80</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>80</v>
@@ -7425,19 +7195,19 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>80</v>
+        <v>122</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>80</v>
@@ -7463,14 +7233,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>113</v>
+        <v>327</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7483,24 +7253,26 @@
         <v>80</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K43" t="s" s="2">
         <v>114</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>115</v>
+        <v>328</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>116</v>
+        <v>329</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="O43" s="2"/>
+      <c r="O43" t="s" s="2">
+        <v>330</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>80</v>
       </c>
@@ -7536,19 +7308,19 @@
         <v>80</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>121</v>
+        <v>331</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7569,7 +7341,7 @@
         <v>80</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>111</v>
+        <v>192</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>80</v>
@@ -7586,10 +7358,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7612,20 +7384,16 @@
         <v>94</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>135</v>
+        <v>389</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>396</v>
-      </c>
+        <v>391</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>80</v>
       </c>
@@ -7634,7 +7402,7 @@
         <v>80</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>397</v>
+        <v>80</v>
       </c>
       <c r="T44" t="s" s="2">
         <v>80</v>
@@ -7673,10 +7441,10 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>93</v>
@@ -7691,30 +7459,30 @@
         <v>80</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>80</v>
+        <v>392</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>399</v>
+        <v>384</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>80</v>
+        <v>393</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>80</v>
+        <v>395</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7734,20 +7502,18 @@
         <v>80</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K45" t="s" s="2">
         <v>107</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>403</v>
+        <v>108</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>405</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>80</v>
@@ -7796,7 +7562,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>406</v>
+        <v>110</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7808,7 +7574,7 @@
         <v>80</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>80</v>
@@ -7817,7 +7583,7 @@
         <v>80</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>407</v>
+        <v>111</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>80</v>
@@ -7826,7 +7592,7 @@
         <v>80</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>408</v>
+        <v>80</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>80</v>
@@ -7834,21 +7600,21 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>409</v>
+        <v>397</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>410</v>
+        <v>397</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>80</v>
@@ -7857,21 +7623,21 @@
         <v>80</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>169</v>
+        <v>114</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>411</v>
+        <v>115</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" t="s" s="2">
-        <v>413</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>80</v>
       </c>
@@ -7907,31 +7673,31 @@
         <v>80</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>414</v>
+        <v>121</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>80</v>
@@ -7940,7 +7706,7 @@
         <v>80</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>250</v>
+        <v>111</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>80</v>
@@ -7949,7 +7715,7 @@
         <v>80</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>415</v>
+        <v>80</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>80</v>
@@ -7957,10 +7723,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>416</v>
+        <v>398</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>417</v>
+        <v>398</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7968,7 +7734,7 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>93</v>
@@ -7983,17 +7749,17 @@
         <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>107</v>
+        <v>169</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>418</v>
+        <v>399</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>419</v>
+        <v>400</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>420</v>
+        <v>401</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>80</v>
@@ -8006,7 +7772,7 @@
         <v>80</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>80</v>
+        <v>402</v>
       </c>
       <c r="U47" t="s" s="2">
         <v>80</v>
@@ -8018,13 +7784,13 @@
         <v>80</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>80</v>
+        <v>224</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>80</v>
+        <v>403</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>80</v>
+        <v>404</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>80</v>
@@ -8042,7 +7808,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>421</v>
+        <v>405</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -8063,7 +7829,7 @@
         <v>80</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>422</v>
+        <v>406</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>80</v>
@@ -8072,18 +7838,18 @@
         <v>80</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>423</v>
+        <v>407</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
-        <v>424</v>
+        <v>408</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>425</v>
+        <v>408</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8097,7 +7863,7 @@
         <v>93</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>80</v>
@@ -8106,19 +7872,17 @@
         <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>426</v>
+        <v>169</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>427</v>
+        <v>409</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>429</v>
-      </c>
+        <v>410</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>430</v>
+        <v>411</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>80</v>
@@ -8131,7 +7895,7 @@
         <v>80</v>
       </c>
       <c r="T48" t="s" s="2">
-        <v>80</v>
+        <v>412</v>
       </c>
       <c r="U48" t="s" s="2">
         <v>80</v>
@@ -8143,13 +7907,13 @@
         <v>80</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>80</v>
+        <v>173</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>80</v>
+        <v>174</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>80</v>
+        <v>175</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>80</v>
@@ -8167,7 +7931,7 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>431</v>
+        <v>413</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -8188,7 +7952,7 @@
         <v>80</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>432</v>
+        <v>414</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>80</v>
@@ -8197,7 +7961,7 @@
         <v>80</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>433</v>
+        <v>80</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>80</v>
@@ -8205,10 +7969,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>434</v>
+        <v>415</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>435</v>
+        <v>415</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8216,7 +7980,7 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>93</v>
@@ -8228,22 +7992,22 @@
         <v>80</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>107</v>
+        <v>416</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>436</v>
+        <v>417</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>437</v>
+        <v>418</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>438</v>
+        <v>419</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>439</v>
+        <v>420</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>80</v>
@@ -8292,7 +8056,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>440</v>
+        <v>421</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8313,7 +8077,7 @@
         <v>80</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>441</v>
+        <v>422</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>80</v>
@@ -8322,22 +8086,20 @@
         <v>80</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>442</v>
+        <v>423</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>443</v>
+        <v>424</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="C50" t="s" s="2">
-        <v>444</v>
-      </c>
+        <v>424</v>
+      </c>
+      <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
         <v>80</v>
       </c>
@@ -8346,10 +8108,10 @@
         <v>81</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>80</v>
@@ -8358,19 +8120,19 @@
         <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>242</v>
+        <v>425</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>445</v>
+        <v>426</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>360</v>
+        <v>427</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>361</v>
+        <v>428</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>362</v>
+        <v>429</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>80</v>
@@ -8383,7 +8145,7 @@
         <v>80</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>80</v>
+        <v>430</v>
       </c>
       <c r="U50" t="s" s="2">
         <v>80</v>
@@ -8395,11 +8157,13 @@
         <v>80</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="Y50" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="Z50" t="s" s="2">
-        <v>446</v>
+        <v>80</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>80</v>
@@ -8417,13 +8181,13 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>358</v>
+        <v>431</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>80</v>
@@ -8435,30 +8199,30 @@
         <v>80</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>365</v>
+        <v>80</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>366</v>
+        <v>432</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>367</v>
+        <v>80</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>368</v>
+        <v>433</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>369</v>
+        <v>80</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>375</v>
+        <v>434</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8478,19 +8242,23 @@
         <v>80</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>107</v>
+        <v>435</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>108</v>
+        <v>436</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+        <v>437</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>439</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>80</v>
       </c>
@@ -8538,7 +8306,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>110</v>
+        <v>440</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8550,7 +8318,7 @@
         <v>80</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>80</v>
@@ -8559,7 +8327,7 @@
         <v>80</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>111</v>
+        <v>441</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>80</v>
@@ -8576,21 +8344,21 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>377</v>
+        <v>442</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>80</v>
@@ -8599,21 +8367,23 @@
         <v>80</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>114</v>
+        <v>416</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>115</v>
+        <v>443</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>116</v>
+        <v>444</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O52" s="2"/>
+        <v>445</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>446</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>80</v>
       </c>
@@ -8649,31 +8419,31 @@
         <v>80</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>121</v>
+        <v>447</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>80</v>
@@ -8682,7 +8452,7 @@
         <v>80</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>111</v>
+        <v>448</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>80</v>
@@ -8702,7 +8472,7 @@
         <v>449</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>379</v>
+        <v>449</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8710,10 +8480,10 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>80</v>
@@ -8725,19 +8495,17 @@
         <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>147</v>
+        <v>107</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>380</v>
+        <v>450</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>382</v>
-      </c>
+        <v>451</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>383</v>
+        <v>452</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>80</v>
@@ -8750,7 +8518,7 @@
         <v>80</v>
       </c>
       <c r="T53" t="s" s="2">
-        <v>80</v>
+        <v>453</v>
       </c>
       <c r="U53" t="s" s="2">
         <v>80</v>
@@ -8786,13 +8554,13 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>384</v>
+        <v>454</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>80</v>
@@ -8807,7 +8575,7 @@
         <v>80</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>385</v>
+        <v>455</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>80</v>
@@ -8816,18 +8584,18 @@
         <v>80</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>386</v>
+        <v>80</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>388</v>
+        <v>456</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8841,25 +8609,27 @@
         <v>93</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>107</v>
+        <v>457</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>108</v>
+        <v>458</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>109</v>
+        <v>459</v>
       </c>
       <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
+      <c r="O54" t="s" s="2">
+        <v>460</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>80</v>
       </c>
@@ -8907,7 +8677,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>110</v>
+        <v>461</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8919,7 +8689,7 @@
         <v>80</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>80</v>
@@ -8928,7 +8698,7 @@
         <v>80</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>111</v>
+        <v>441</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>80</v>
@@ -8943,44 +8713,44 @@
         <v>80</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
-        <v>451</v>
+        <v>462</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>390</v>
+        <v>462</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>114</v>
+        <v>147</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>115</v>
+        <v>463</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>116</v>
+        <v>464</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>117</v>
+        <v>465</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9006,55 +8776,53 @@
         <v>80</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>80</v>
+        <v>466</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="AD55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>121</v>
+        <v>462</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>122</v>
+        <v>467</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>80</v>
+        <v>468</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>111</v>
+        <v>384</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>80</v>
+        <v>469</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>80</v>
@@ -9063,15 +8831,15 @@
         <v>80</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>80</v>
+        <v>470</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
-        <v>452</v>
+        <v>471</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>392</v>
+        <v>471</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9079,13 +8847,13 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>80</v>
@@ -9094,20 +8862,18 @@
         <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>135</v>
+        <v>316</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>393</v>
+        <v>472</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>394</v>
+        <v>473</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>396</v>
-      </c>
+        <v>474</v>
+      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>80</v>
       </c>
@@ -9116,7 +8882,7 @@
         <v>80</v>
       </c>
       <c r="S56" t="s" s="2">
-        <v>453</v>
+        <v>80</v>
       </c>
       <c r="T56" t="s" s="2">
         <v>80</v>
@@ -9155,7 +8921,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>398</v>
+        <v>471</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -9176,7 +8942,7 @@
         <v>80</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>399</v>
+        <v>475</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>80</v>
@@ -9185,7 +8951,7 @@
         <v>80</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>400</v>
+        <v>80</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>80</v>
@@ -9193,10 +8959,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>454</v>
+        <v>476</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>402</v>
+        <v>476</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9216,20 +8982,18 @@
         <v>80</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K57" t="s" s="2">
         <v>107</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>403</v>
+        <v>108</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>405</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>80</v>
@@ -9278,7 +9042,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>406</v>
+        <v>110</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9290,7 +9054,7 @@
         <v>80</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>80</v>
@@ -9299,7 +9063,7 @@
         <v>80</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>407</v>
+        <v>111</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>80</v>
@@ -9308,7 +9072,7 @@
         <v>80</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>408</v>
+        <v>80</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>80</v>
@@ -9316,21 +9080,21 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>455</v>
+        <v>477</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>410</v>
+        <v>477</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>80</v>
@@ -9339,21 +9103,21 @@
         <v>80</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>169</v>
+        <v>114</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>411</v>
+        <v>115</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="N58" s="2"/>
-      <c r="O58" t="s" s="2">
-        <v>413</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>80</v>
       </c>
@@ -9401,19 +9165,19 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>414</v>
+        <v>121</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>80</v>
@@ -9422,7 +9186,7 @@
         <v>80</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>250</v>
+        <v>111</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>80</v>
@@ -9431,7 +9195,7 @@
         <v>80</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>415</v>
+        <v>80</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>80</v>
@@ -9439,43 +9203,45 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>456</v>
+        <v>478</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>417</v>
+        <v>478</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>80</v>
+        <v>327</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="J59" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>418</v>
+        <v>328</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="N59" s="2"/>
+        <v>329</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O59" t="s" s="2">
-        <v>420</v>
+        <v>330</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>80</v>
@@ -9524,19 +9290,19 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>421</v>
+        <v>331</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>80</v>
@@ -9545,7 +9311,7 @@
         <v>80</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>422</v>
+        <v>192</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>80</v>
@@ -9554,7 +9320,7 @@
         <v>80</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>423</v>
+        <v>80</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>80</v>
@@ -9562,10 +9328,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>457</v>
+        <v>479</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>425</v>
+        <v>479</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9576,7 +9342,7 @@
         <v>81</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>80</v>
@@ -9585,23 +9351,19 @@
         <v>80</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>426</v>
+        <v>480</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>427</v>
+        <v>481</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>430</v>
-      </c>
+        <v>482</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>80</v>
       </c>
@@ -9649,13 +9411,13 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>431</v>
+        <v>479</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>80</v>
@@ -9664,22 +9426,22 @@
         <v>105</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>80</v>
+        <v>483</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>80</v>
+        <v>484</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>432</v>
+        <v>485</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>80</v>
+        <v>486</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>433</v>
+        <v>80</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>80</v>
@@ -9687,10 +9449,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>458</v>
+        <v>487</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>435</v>
+        <v>487</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9710,23 +9472,21 @@
         <v>80</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>107</v>
+        <v>242</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>436</v>
+        <v>488</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>437</v>
+        <v>489</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>439</v>
-      </c>
+        <v>490</v>
+      </c>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>80</v>
       </c>
@@ -9750,13 +9510,13 @@
         <v>80</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>80</v>
+        <v>159</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>80</v>
+        <v>491</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>80</v>
+        <v>492</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>80</v>
@@ -9774,28 +9534,28 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>440</v>
+        <v>487</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>105</v>
+        <v>493</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>80</v>
+        <v>494</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>441</v>
+        <v>495</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>80</v>
@@ -9804,18 +9564,18 @@
         <v>80</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>442</v>
+        <v>80</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>80</v>
+        <v>496</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>459</v>
+        <v>497</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>459</v>
+        <v>497</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9823,7 +9583,7 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G62" t="s" s="2">
         <v>93</v>
@@ -9838,13 +9598,13 @@
         <v>94</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>316</v>
+        <v>498</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>460</v>
+        <v>499</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>461</v>
+        <v>500</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9895,13 +9655,13 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>459</v>
+        <v>497</v>
       </c>
       <c r="AG62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH62" t="s" s="2">
         <v>93</v>
-      </c>
-      <c r="AH62" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>80</v>
@@ -9913,13 +9673,13 @@
         <v>80</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>462</v>
+        <v>501</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>463</v>
+        <v>502</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>80</v>
+        <v>503</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>80</v>
@@ -9928,15 +9688,15 @@
         <v>80</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>80</v>
+        <v>504</v>
       </c>
     </row>
-    <row r="63" hidden="true">
+    <row r="63">
       <c r="A63" t="s" s="2">
-        <v>464</v>
+        <v>505</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>464</v>
+        <v>505</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9950,7 +9710,7 @@
         <v>93</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>80</v>
@@ -9959,13 +9719,13 @@
         <v>80</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>107</v>
+        <v>242</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>108</v>
+        <v>506</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>109</v>
+        <v>507</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9992,13 +9752,11 @@
         <v>80</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="Y63" s="2"/>
       <c r="Z63" t="s" s="2">
-        <v>80</v>
+        <v>508</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>80</v>
@@ -10016,7 +9774,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>110</v>
+        <v>505</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -10028,19 +9786,19 @@
         <v>80</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>80</v>
+        <v>509</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>80</v>
+        <v>510</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>111</v>
+        <v>511</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>80</v>
+        <v>512</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>80</v>
@@ -10049,29 +9807,29 @@
         <v>80</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>80</v>
+        <v>513</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
-        <v>465</v>
+        <v>514</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>465</v>
+        <v>514</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>80</v>
@@ -10080,18 +9838,20 @@
         <v>80</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>114</v>
+        <v>242</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>115</v>
+        <v>515</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>116</v>
+        <v>516</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O64" s="2"/>
+        <v>517</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>518</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>80</v>
       </c>
@@ -10115,13 +9875,11 @@
         <v>80</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y64" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="Y64" s="2"/>
       <c r="Z64" t="s" s="2">
-        <v>80</v>
+        <v>519</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>80</v>
@@ -10139,31 +9897,31 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>121</v>
+        <v>514</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>122</v>
+        <v>509</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>80</v>
+        <v>510</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>111</v>
+        <v>511</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>80</v>
+        <v>510</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>80</v>
@@ -10172,51 +9930,47 @@
         <v>80</v>
       </c>
       <c r="AQ64" t="s" s="2">
-        <v>80</v>
+        <v>520</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
-        <v>466</v>
+        <v>521</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>466</v>
+        <v>521</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>327</v>
+        <v>80</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>114</v>
+        <v>267</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>328</v>
+        <v>522</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>523</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>80</v>
       </c>
@@ -10264,31 +10018,31 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>331</v>
+        <v>521</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>80</v>
+        <v>271</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>192</v>
+        <v>272</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>80</v>
+        <v>273</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>80</v>
@@ -10297,15 +10051,15 @@
         <v>80</v>
       </c>
       <c r="AQ65" t="s" s="2">
-        <v>80</v>
+        <v>524</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>467</v>
+        <v>525</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>467</v>
+        <v>525</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10313,10 +10067,10 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>80</v>
@@ -10325,18 +10079,20 @@
         <v>80</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>468</v>
+        <v>526</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>469</v>
+        <v>527</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>528</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>529</v>
+      </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>80</v>
@@ -10385,13 +10141,13 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>467</v>
+        <v>525</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>80</v>
@@ -10403,2726 +10159,26 @@
         <v>80</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>471</v>
+        <v>530</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>463</v>
+        <v>531</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>472</v>
+        <v>532</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>473</v>
+        <v>80</v>
       </c>
       <c r="AQ66" t="s" s="2">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="67" hidden="true">
-      <c r="A67" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="C67" s="2"/>
-      <c r="D67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E67" s="2"/>
-      <c r="F67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G67" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K67" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="L67" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N67" s="2"/>
-      <c r="O67" s="2"/>
-      <c r="P67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q67" s="2"/>
-      <c r="R67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="AG67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH67" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ67" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="68" hidden="true">
-      <c r="A68" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="C68" s="2"/>
-      <c r="D68" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="E68" s="2"/>
-      <c r="F68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K68" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="L68" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O68" s="2"/>
-      <c r="P68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q68" s="2"/>
-      <c r="R68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="AG68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ68" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AK68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ68" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="69" hidden="true">
-      <c r="A69" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="C69" s="2"/>
-      <c r="D69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E69" s="2"/>
-      <c r="F69" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="G69" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J69" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K69" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="L69" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="P69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q69" s="2"/>
-      <c r="R69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T69" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="U69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X69" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="Y69" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="Z69" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="AG69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH69" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ69" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP69" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="AQ69" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="C70" s="2"/>
-      <c r="D70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E70" s="2"/>
-      <c r="F70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G70" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H70" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="I70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J70" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K70" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="L70" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="N70" s="2"/>
-      <c r="O70" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="P70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q70" s="2"/>
-      <c r="R70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T70" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="U70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X70" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="Y70" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="Z70" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="AA70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="AG70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH70" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ70" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM70" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ70" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="71" hidden="true">
-      <c r="A71" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="C71" s="2"/>
-      <c r="D71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E71" s="2"/>
-      <c r="F71" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="G71" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K71" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="L71" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="P71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q71" s="2"/>
-      <c r="R71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="AG71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH71" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ71" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP71" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="AQ71" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="72" hidden="true">
-      <c r="A72" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="C72" s="2"/>
-      <c r="D72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E72" s="2"/>
-      <c r="F72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J72" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K72" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="L72" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="P72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q72" s="2"/>
-      <c r="R72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T72" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="U72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="AG72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH72" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ72" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP72" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="AQ72" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="73" hidden="true">
-      <c r="A73" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="C73" s="2"/>
-      <c r="D73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E73" s="2"/>
-      <c r="F73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G73" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J73" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K73" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="L73" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="P73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q73" s="2"/>
-      <c r="R73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="AG73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH73" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ73" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ73" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="74" hidden="true">
-      <c r="A74" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="C74" s="2"/>
-      <c r="D74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E74" s="2"/>
-      <c r="F74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G74" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J74" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K74" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="L74" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="P74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q74" s="2"/>
-      <c r="R74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="AG74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH74" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ74" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ74" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="75" hidden="true">
-      <c r="A75" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="B75" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="C75" s="2"/>
-      <c r="D75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E75" s="2"/>
-      <c r="F75" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="G75" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J75" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K75" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="L75" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="N75" s="2"/>
-      <c r="O75" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="P75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q75" s="2"/>
-      <c r="R75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T75" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="U75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF75" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="AG75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH75" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ75" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ75" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="B76" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="C76" s="2"/>
-      <c r="D76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E76" s="2"/>
-      <c r="F76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G76" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H76" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="I76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J76" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K76" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="L76" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="N76" s="2"/>
-      <c r="O76" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="P76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q76" s="2"/>
-      <c r="R76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="AG76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH76" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ76" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ76" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="C77" s="2"/>
-      <c r="D77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E77" s="2"/>
-      <c r="F77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G77" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H77" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="I77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J77" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K77" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="L77" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="O77" s="2"/>
-      <c r="P77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q77" s="2"/>
-      <c r="R77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X77" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="Y77" s="2"/>
-      <c r="Z77" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="AG77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH77" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ77" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="AK77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL77" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="AM77" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="AO77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ77" t="s" s="2">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="B78" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="C78" s="2"/>
-      <c r="D78" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E78" s="2"/>
-      <c r="F78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G78" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H78" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="I78" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J78" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K78" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="L78" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="O78" s="2"/>
-      <c r="P78" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q78" s="2"/>
-      <c r="R78" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S78" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T78" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U78" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V78" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W78" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X78" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z78" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA78" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB78" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD78" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE78" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF78" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="AG78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH78" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI78" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ78" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK78" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL78" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM78" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO78" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP78" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ78" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="79" hidden="true">
-      <c r="A79" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="C79" s="2"/>
-      <c r="D79" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E79" s="2"/>
-      <c r="F79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G79" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H79" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I79" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J79" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K79" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="L79" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N79" s="2"/>
-      <c r="O79" s="2"/>
-      <c r="P79" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q79" s="2"/>
-      <c r="R79" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S79" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T79" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U79" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V79" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W79" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X79" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y79" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z79" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA79" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB79" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC79" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD79" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE79" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF79" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="AG79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH79" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI79" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ79" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK79" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL79" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM79" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="AN79" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO79" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP79" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ79" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="80" hidden="true">
-      <c r="A80" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="B80" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="C80" s="2"/>
-      <c r="D80" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="E80" s="2"/>
-      <c r="F80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K80" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="L80" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O80" s="2"/>
-      <c r="P80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q80" s="2"/>
-      <c r="R80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="AG80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ80" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AK80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ80" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="81" hidden="true">
-      <c r="A81" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="B81" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="C81" s="2"/>
-      <c r="D81" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="E81" s="2"/>
-      <c r="F81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H81" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I81" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="J81" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K81" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="L81" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="P81" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q81" s="2"/>
-      <c r="R81" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S81" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T81" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U81" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V81" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W81" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X81" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y81" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z81" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA81" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB81" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC81" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD81" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE81" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF81" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="AG81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI81" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ81" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AK81" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL81" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM81" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO81" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP81" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ81" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="82" hidden="true">
-      <c r="A82" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="B82" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="C82" s="2"/>
-      <c r="D82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E82" s="2"/>
-      <c r="F82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K82" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="L82" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="N82" s="2"/>
-      <c r="O82" s="2"/>
-      <c r="P82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q82" s="2"/>
-      <c r="R82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="AG82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ82" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK82" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="AL82" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="AM82" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO82" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="AP82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ82" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="83" hidden="true">
-      <c r="A83" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="B83" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="C83" s="2"/>
-      <c r="D83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E83" s="2"/>
-      <c r="F83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G83" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K83" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="L83" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="O83" s="2"/>
-      <c r="P83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q83" s="2"/>
-      <c r="R83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X83" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="Y83" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="Z83" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="AA83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF83" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="AG83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ83" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="AK83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL83" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="AM83" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ83" t="s" s="2">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="B84" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="C84" s="2"/>
-      <c r="D84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E84" s="2"/>
-      <c r="F84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G84" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H84" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="I84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J84" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K84" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="L84" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="N84" s="2"/>
-      <c r="O84" s="2"/>
-      <c r="P84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q84" s="2"/>
-      <c r="R84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF84" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="AG84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH84" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ84" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL84" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="AM84" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="AO84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ84" t="s" s="2">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="B85" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="C85" s="2"/>
-      <c r="D85" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E85" s="2"/>
-      <c r="F85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G85" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H85" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="I85" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J85" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K85" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="L85" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="N85" s="2"/>
-      <c r="O85" s="2"/>
-      <c r="P85" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q85" s="2"/>
-      <c r="R85" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S85" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T85" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U85" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V85" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W85" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X85" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="Y85" s="2"/>
-      <c r="Z85" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="AA85" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB85" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC85" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD85" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE85" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF85" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="AG85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH85" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI85" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ85" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="AK85" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL85" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="AM85" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="AN85" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="AO85" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP85" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ85" t="s" s="2">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="B86" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="C86" s="2"/>
-      <c r="D86" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E86" s="2"/>
-      <c r="F86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G86" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H86" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="I86" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J86" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K86" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="L86" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="P86" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q86" s="2"/>
-      <c r="R86" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S86" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T86" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U86" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V86" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W86" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X86" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="Y86" s="2"/>
-      <c r="Z86" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="AA86" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB86" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC86" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD86" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE86" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF86" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="AG86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH86" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI86" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ86" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="AK86" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL86" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="AM86" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="AN86" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="AO86" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP86" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ86" t="s" s="2">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="B87" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="C87" s="2"/>
-      <c r="D87" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E87" s="2"/>
-      <c r="F87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G87" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H87" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="I87" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J87" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K87" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="L87" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="N87" s="2"/>
-      <c r="O87" s="2"/>
-      <c r="P87" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q87" s="2"/>
-      <c r="R87" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S87" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T87" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U87" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V87" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W87" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X87" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y87" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z87" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA87" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB87" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC87" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD87" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE87" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF87" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="AG87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH87" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI87" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ87" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK87" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL87" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="AM87" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="AN87" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="AO87" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP87" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ87" t="s" s="2">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="88" hidden="true">
-      <c r="A88" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="B88" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="C88" s="2"/>
-      <c r="D88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E88" s="2"/>
-      <c r="F88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K88" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="L88" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="O88" s="2"/>
-      <c r="P88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q88" s="2"/>
-      <c r="R88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF88" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="AG88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ88" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL88" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="AM88" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="AO88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ88" t="s" s="2">
-        <v>612</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AQ88">
+  <autoFilter ref="A1:AQ66">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -13132,7 +10188,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI87">
+  <conditionalFormatting sqref="A2:AI65">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-simplified-publish.xlsx
+++ b/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-simplified-publish.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:28:00+00:00</t>
+    <t>2026-08-06T13:33:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1158,7 +1158,7 @@
     <t>Use of the Health Care Privacy/Security Classification (HCS) system of security-tag use is recommended.</t>
   </si>
   <si>
-    <t xml:space="preserve">pattern:$this}
+    <t xml:space="preserve">value:$this}
 </t>
   </si>
   <si>

--- a/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-simplified-publish.xlsx
+++ b/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-simplified-publish.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2607" uniqueCount="534">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2607" uniqueCount="533">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:33:58+00:00</t>
+    <t>2026-08-06T13:37:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1162,7 +1162,7 @@
 </t>
   </si>
   <si>
-    <t>Slice sur securityLabel (pattern sur coding.system) pour distinguer le niveau de confidentialité (NRV) du statut de visibilité complémentaire (TRE A07)</t>
+    <t>Slice sur securityLabel pour distinguer le niveau de confidentialité (NRV) du statut de visibilité complémentaire (TRE A07) : confidentiality est discriminée par son required binding (ValueSet fermé v3-ConfidentialityClassification), visibilityStatus par un pattern sur coding.system (JDV_J110-StatutVisibiliteDocument-CISIS)</t>
   </si>
   <si>
     <t>Composition.confidentiality, Composition.meta.security</t>
@@ -1187,13 +1187,6 @@
   </si>
   <si>
     <t>Niveau de confidentialité standard du document (Normal, Restreint, Très restreint).</t>
-  </si>
-  <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;system value="http://terminology.hl7.org/CodeSystem/v3-Confidentiality"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
     <t>http://terminology.hl7.org/ValueSet/v3-ConfidentialityClassification</t>
@@ -2051,7 +2044,7 @@
     <col min="26" max="26" width="102.93359375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="119.3046875" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="253.52734375" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="37.78125" customWidth="true" bestFit="true" hidden="true"/>
@@ -6668,7 +6661,7 @@
         <v>80</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>373</v>
+        <v>80</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>80</v>
@@ -6687,7 +6680,7 @@
       </c>
       <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>80</v>
@@ -6743,13 +6736,13 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>358</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>80</v>
@@ -6774,7 +6767,7 @@
         <v>242</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M39" t="s" s="2">
         <v>360</v>
@@ -6793,7 +6786,7 @@
         <v>80</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="T39" t="s" s="2">
         <v>80</v>
@@ -6812,7 +6805,7 @@
       </c>
       <c r="Y39" s="2"/>
       <c r="Z39" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>80</v>
@@ -6868,10 +6861,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6897,10 +6890,10 @@
         <v>316</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>382</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6951,7 +6944,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>93</v>
@@ -6969,10 +6962,10 @@
         <v>80</v>
       </c>
       <c r="AL40" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AM40" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>80</v>
@@ -6989,10 +6982,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7110,10 +7103,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7233,10 +7226,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7358,10 +7351,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7384,13 +7377,13 @@
         <v>94</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>391</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7441,7 +7434,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>93</v>
@@ -7459,30 +7452,30 @@
         <v>80</v>
       </c>
       <c r="AL44" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="AM44" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="AN44" t="s" s="2">
+      <c r="AO44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP44" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="AO44" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP44" t="s" s="2">
+      <c r="AQ44" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="AQ44" t="s" s="2">
-        <v>395</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7600,10 +7593,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7723,10 +7716,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7752,14 +7745,14 @@
         <v>169</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>80</v>
@@ -7772,7 +7765,7 @@
         <v>80</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="U47" t="s" s="2">
         <v>80</v>
@@ -7787,28 +7780,28 @@
         <v>224</v>
       </c>
       <c r="Y47" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="Z47" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="Z47" t="s" s="2">
+      <c r="AA47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF47" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="AA47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF47" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7829,16 +7822,16 @@
         <v>80</v>
       </c>
       <c r="AM47" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP47" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP47" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>80</v>
@@ -7846,10 +7839,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7875,14 +7868,14 @@
         <v>169</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>80</v>
@@ -7895,7 +7888,7 @@
         <v>80</v>
       </c>
       <c r="T48" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="U48" t="s" s="2">
         <v>80</v>
@@ -7931,7 +7924,7 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7952,7 +7945,7 @@
         <v>80</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>80</v>
@@ -7969,10 +7962,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7995,19 +7988,19 @@
         <v>80</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="N49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>80</v>
@@ -8056,7 +8049,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8077,16 +8070,16 @@
         <v>80</v>
       </c>
       <c r="AM49" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP49" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP49" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>80</v>
@@ -8094,10 +8087,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8120,19 +8113,19 @@
         <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="N50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>80</v>
@@ -8145,43 +8138,43 @@
         <v>80</v>
       </c>
       <c r="T50" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF50" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="U50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8202,16 +8195,16 @@
         <v>80</v>
       </c>
       <c r="AM50" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP50" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP50" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>80</v>
@@ -8219,10 +8212,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8245,19 +8238,19 @@
         <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="N51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>80</v>
@@ -8306,7 +8299,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8327,7 +8320,7 @@
         <v>80</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>80</v>
@@ -8344,10 +8337,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8370,19 +8363,19 @@
         <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="N52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>80</v>
@@ -8431,7 +8424,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8452,7 +8445,7 @@
         <v>80</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>80</v>
@@ -8469,10 +8462,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8498,14 +8491,14 @@
         <v>107</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>80</v>
@@ -8518,43 +8511,43 @@
         <v>80</v>
       </c>
       <c r="T53" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF53" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="U53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8575,7 +8568,7 @@
         <v>80</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>80</v>
@@ -8592,10 +8585,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8618,17 +8611,17 @@
         <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>80</v>
@@ -8677,7 +8670,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8698,7 +8691,7 @@
         <v>80</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>80</v>
@@ -8715,10 +8708,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8744,13 +8737,13 @@
         <v>147</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8780,7 +8773,7 @@
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>80</v>
@@ -8798,7 +8791,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8810,36 +8803,36 @@
         <v>80</v>
       </c>
       <c r="AJ55" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL55" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="AK55" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL55" t="s" s="2">
+      <c r="AM55" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AN55" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="AM55" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="AN55" t="s" s="2">
+      <c r="AO55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ55" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP55" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ55" t="s" s="2">
-        <v>470</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8865,13 +8858,13 @@
         <v>316</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8921,7 +8914,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8942,7 +8935,7 @@
         <v>80</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>80</v>
@@ -8959,10 +8952,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9080,10 +9073,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9203,10 +9196,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9328,10 +9321,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9354,13 +9347,13 @@
         <v>80</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>480</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>481</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>482</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9411,7 +9404,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9426,19 +9419,19 @@
         <v>105</v>
       </c>
       <c r="AK60" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="AL60" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="AL60" t="s" s="2">
+      <c r="AM60" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="AM60" t="s" s="2">
+      <c r="AN60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO60" t="s" s="2">
         <v>485</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>486</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>80</v>
@@ -9449,10 +9442,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9478,13 +9471,13 @@
         <v>242</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9513,11 +9506,11 @@
         <v>159</v>
       </c>
       <c r="Y61" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="Z61" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="Z61" t="s" s="2">
-        <v>492</v>
-      </c>
       <c r="AA61" t="s" s="2">
         <v>80</v>
       </c>
@@ -9534,7 +9527,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9546,36 +9539,36 @@
         <v>80</v>
       </c>
       <c r="AJ61" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL61" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="AK61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL61" t="s" s="2">
+      <c r="AM61" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="AM61" t="s" s="2">
+      <c r="AN61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ61" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ61" t="s" s="2">
-        <v>496</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9598,13 +9591,13 @@
         <v>94</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>499</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>500</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9655,7 +9648,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9673,30 +9666,30 @@
         <v>80</v>
       </c>
       <c r="AL62" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="AM62" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="AM62" t="s" s="2">
+      <c r="AN62" t="s" s="2">
         <v>502</v>
       </c>
-      <c r="AN62" t="s" s="2">
+      <c r="AO62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ62" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="AO62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ62" t="s" s="2">
-        <v>504</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9722,10 +9715,10 @@
         <v>242</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>507</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9756,7 +9749,7 @@
       </c>
       <c r="Y63" s="2"/>
       <c r="Z63" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>80</v>
@@ -9774,7 +9767,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9786,36 +9779,36 @@
         <v>80</v>
       </c>
       <c r="AJ63" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL63" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="AK63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL63" t="s" s="2">
+      <c r="AM63" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="AM63" t="s" s="2">
+      <c r="AN63" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="AN63" t="s" s="2">
+      <c r="AO63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ63" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ63" t="s" s="2">
-        <v>513</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9841,16 +9834,16 @@
         <v>242</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>516</v>
       </c>
-      <c r="N64" t="s" s="2">
+      <c r="O64" t="s" s="2">
         <v>517</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>80</v>
@@ -9879,7 +9872,7 @@
       </c>
       <c r="Y64" s="2"/>
       <c r="Z64" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>80</v>
@@ -9897,7 +9890,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9909,19 +9902,19 @@
         <v>80</v>
       </c>
       <c r="AJ64" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL64" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="AK64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL64" t="s" s="2">
+      <c r="AM64" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="AM64" t="s" s="2">
-        <v>511</v>
-      </c>
       <c r="AN64" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>80</v>
@@ -9930,15 +9923,15 @@
         <v>80</v>
       </c>
       <c r="AQ64" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9964,10 +9957,10 @@
         <v>267</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>523</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10018,7 +10011,7 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10051,15 +10044,15 @@
         <v>80</v>
       </c>
       <c r="AQ65" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10082,16 +10075,16 @@
         <v>80</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="L66" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="M66" t="s" s="2">
         <v>527</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>528</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>529</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10141,7 +10134,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10159,22 +10152,22 @@
         <v>80</v>
       </c>
       <c r="AL66" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="AM66" t="s" s="2">
         <v>530</v>
       </c>
-      <c r="AM66" t="s" s="2">
+      <c r="AN66" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="AN66" t="s" s="2">
+      <c r="AO66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ66" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ66" t="s" s="2">
-        <v>533</v>
       </c>
     </row>
   </sheetData>

--- a/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-simplified-publish.xlsx
+++ b/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-simplified-publish.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2607" uniqueCount="533">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2607" uniqueCount="532">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:37:30+00:00</t>
+    <t>2026-08-06T13:40:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1162,7 +1162,7 @@
 </t>
   </si>
   <si>
-    <t>Slice sur securityLabel pour distinguer le niveau de confidentialité (NRV) du statut de visibilité complémentaire (TRE A07) : confidentiality est discriminée par son required binding (ValueSet fermé v3-ConfidentialityClassification), visibilityStatus par un pattern sur coding.system (JDV_J110-StatutVisibiliteDocument-CISIS)</t>
+    <t>Slice sur securityLabel pour distinguer le niveau de confidentialité (NRV) du statut de visibilité complémentaire (TRE A07) : chaque slice est discriminée par son required binding sur un ValueSet fermé (v3-ConfidentialityClassification pour confidentiality, JDV_J110-StatutVisibiliteDocument-CISIS pour visibilityStatus)</t>
   </si>
   <si>
     <t>Composition.confidentiality, Composition.meta.security</t>
@@ -1199,13 +1199,6 @@
   </si>
   <si>
     <t>Statut de visibilité complémentaire du document (motifs de masquage patient, représentants légaux, professionnels).</t>
-  </si>
-  <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;system value="https://mos.esante.gouv.fr/NOS/TRE_A07-StatutVisibiliteDocument/FHIR/TRE-A07-StatutVisibiliteDocument"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J110-StatutVisibiliteDocument-CISIS/FHIR/JDV-J110-StatutVisibiliteDocument-CISIS</t>
@@ -2044,7 +2037,7 @@
     <col min="26" max="26" width="102.93359375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="253.52734375" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="249.46875" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="37.78125" customWidth="true" bestFit="true" hidden="true"/>
@@ -6786,7 +6779,7 @@
         <v>80</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>377</v>
+        <v>80</v>
       </c>
       <c r="T39" t="s" s="2">
         <v>80</v>
@@ -6805,7 +6798,7 @@
       </c>
       <c r="Y39" s="2"/>
       <c r="Z39" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>80</v>
@@ -6861,10 +6854,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6890,10 +6883,10 @@
         <v>316</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6944,7 +6937,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>93</v>
@@ -6962,10 +6955,10 @@
         <v>80</v>
       </c>
       <c r="AL40" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AM40" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>80</v>
@@ -6982,10 +6975,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7103,10 +7096,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7226,10 +7219,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7351,10 +7344,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7377,13 +7370,13 @@
         <v>94</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7434,7 +7427,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>93</v>
@@ -7452,30 +7445,30 @@
         <v>80</v>
       </c>
       <c r="AL44" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="AM44" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="AN44" t="s" s="2">
+      <c r="AO44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP44" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="AO44" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP44" t="s" s="2">
+      <c r="AQ44" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="AQ44" t="s" s="2">
-        <v>394</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7593,10 +7586,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7716,10 +7709,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7745,14 +7738,14 @@
         <v>169</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>80</v>
@@ -7765,7 +7758,7 @@
         <v>80</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="U47" t="s" s="2">
         <v>80</v>
@@ -7780,28 +7773,28 @@
         <v>224</v>
       </c>
       <c r="Y47" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="Z47" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="Z47" t="s" s="2">
+      <c r="AA47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF47" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="AA47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF47" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7822,16 +7815,16 @@
         <v>80</v>
       </c>
       <c r="AM47" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP47" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP47" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>80</v>
@@ -7839,10 +7832,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7868,14 +7861,14 @@
         <v>169</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>80</v>
@@ -7888,7 +7881,7 @@
         <v>80</v>
       </c>
       <c r="T48" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="U48" t="s" s="2">
         <v>80</v>
@@ -7924,7 +7917,7 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7945,7 +7938,7 @@
         <v>80</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>80</v>
@@ -7962,10 +7955,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7988,19 +7981,19 @@
         <v>80</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="N49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>80</v>
@@ -8049,7 +8042,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8070,16 +8063,16 @@
         <v>80</v>
       </c>
       <c r="AM49" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP49" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP49" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>80</v>
@@ -8087,10 +8080,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8113,19 +8106,19 @@
         <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="N50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>80</v>
@@ -8138,43 +8131,43 @@
         <v>80</v>
       </c>
       <c r="T50" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF50" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="U50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8195,16 +8188,16 @@
         <v>80</v>
       </c>
       <c r="AM50" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP50" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP50" t="s" s="2">
-        <v>432</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>80</v>
@@ -8212,10 +8205,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8238,19 +8231,19 @@
         <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="N51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>80</v>
@@ -8299,7 +8292,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8320,7 +8313,7 @@
         <v>80</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>80</v>
@@ -8337,10 +8330,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8363,19 +8356,19 @@
         <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="N52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>80</v>
@@ -8424,7 +8417,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8445,7 +8438,7 @@
         <v>80</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>80</v>
@@ -8462,10 +8455,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8491,14 +8484,14 @@
         <v>107</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>80</v>
@@ -8511,43 +8504,43 @@
         <v>80</v>
       </c>
       <c r="T53" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF53" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="U53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8568,7 +8561,7 @@
         <v>80</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>80</v>
@@ -8585,10 +8578,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8611,17 +8604,17 @@
         <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>80</v>
@@ -8670,7 +8663,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8691,7 +8684,7 @@
         <v>80</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>80</v>
@@ -8708,10 +8701,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8737,13 +8730,13 @@
         <v>147</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8773,7 +8766,7 @@
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>80</v>
@@ -8791,7 +8784,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8803,36 +8796,36 @@
         <v>80</v>
       </c>
       <c r="AJ55" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL55" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="AK55" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL55" t="s" s="2">
+      <c r="AM55" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AN55" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="AM55" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="AN55" t="s" s="2">
+      <c r="AO55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ55" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP55" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ55" t="s" s="2">
-        <v>469</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8858,13 +8851,13 @@
         <v>316</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8914,7 +8907,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8935,7 +8928,7 @@
         <v>80</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>80</v>
@@ -8952,10 +8945,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9073,10 +9066,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9196,10 +9189,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9321,10 +9314,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9347,13 +9340,13 @@
         <v>80</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>481</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9404,7 +9397,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9419,19 +9412,19 @@
         <v>105</v>
       </c>
       <c r="AK60" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AL60" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="AL60" t="s" s="2">
+      <c r="AM60" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="AM60" t="s" s="2">
+      <c r="AN60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO60" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>485</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>80</v>
@@ -9442,10 +9435,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9471,13 +9464,13 @@
         <v>242</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>489</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9506,11 +9499,11 @@
         <v>159</v>
       </c>
       <c r="Y61" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="Z61" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="Z61" t="s" s="2">
-        <v>491</v>
-      </c>
       <c r="AA61" t="s" s="2">
         <v>80</v>
       </c>
@@ -9527,7 +9520,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9539,36 +9532,36 @@
         <v>80</v>
       </c>
       <c r="AJ61" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL61" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="AK61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL61" t="s" s="2">
+      <c r="AM61" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="AM61" t="s" s="2">
+      <c r="AN61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ61" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ61" t="s" s="2">
-        <v>495</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9591,13 +9584,13 @@
         <v>94</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>499</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9648,7 +9641,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9666,30 +9659,30 @@
         <v>80</v>
       </c>
       <c r="AL62" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AM62" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="AM62" t="s" s="2">
+      <c r="AN62" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="AN62" t="s" s="2">
+      <c r="AO62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ62" t="s" s="2">
         <v>502</v>
-      </c>
-      <c r="AO62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ62" t="s" s="2">
-        <v>503</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9715,10 +9708,10 @@
         <v>242</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>505</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>506</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9749,7 +9742,7 @@
       </c>
       <c r="Y63" s="2"/>
       <c r="Z63" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>80</v>
@@ -9767,7 +9760,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9779,36 +9772,36 @@
         <v>80</v>
       </c>
       <c r="AJ63" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL63" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="AK63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL63" t="s" s="2">
+      <c r="AM63" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="AM63" t="s" s="2">
+      <c r="AN63" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="AN63" t="s" s="2">
+      <c r="AO63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ63" t="s" s="2">
         <v>511</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ63" t="s" s="2">
-        <v>512</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9834,16 +9827,16 @@
         <v>242</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>514</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="N64" t="s" s="2">
+      <c r="O64" t="s" s="2">
         <v>516</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>517</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>80</v>
@@ -9872,7 +9865,7 @@
       </c>
       <c r="Y64" s="2"/>
       <c r="Z64" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>80</v>
@@ -9890,7 +9883,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9902,19 +9895,19 @@
         <v>80</v>
       </c>
       <c r="AJ64" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL64" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="AK64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL64" t="s" s="2">
+      <c r="AM64" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="AM64" t="s" s="2">
-        <v>510</v>
-      </c>
       <c r="AN64" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>80</v>
@@ -9923,15 +9916,15 @@
         <v>80</v>
       </c>
       <c r="AQ64" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9957,10 +9950,10 @@
         <v>267</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>521</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>522</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10011,7 +10004,7 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10044,15 +10037,15 @@
         <v>80</v>
       </c>
       <c r="AQ65" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10075,16 +10068,16 @@
         <v>80</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="L66" t="s" s="2">
         <v>525</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="M66" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10134,7 +10127,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10152,22 +10145,22 @@
         <v>80</v>
       </c>
       <c r="AL66" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="AM66" t="s" s="2">
         <v>529</v>
       </c>
-      <c r="AM66" t="s" s="2">
+      <c r="AN66" t="s" s="2">
         <v>530</v>
       </c>
-      <c r="AN66" t="s" s="2">
+      <c r="AO66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ66" t="s" s="2">
         <v>531</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ66" t="s" s="2">
-        <v>532</v>
       </c>
     </row>
   </sheetData>

--- a/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-simplified-publish.xlsx
+++ b/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-simplified-publish.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2607" uniqueCount="532">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2607" uniqueCount="533">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:40:23+00:00</t>
+    <t>2026-08-06T13:54:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1187,6 +1187,9 @@
   </si>
   <si>
     <t>Niveau de confidentialité standard du document (Normal, Restreint, Très restreint).</t>
+  </si>
+  <si>
+    <t>En l'absence d'information de confidentialité disponible, la valeur par défaut à utiliser est N (Normal), conformément à ce qui est déjà pratiqué aujourd'hui pour les documents CDA.</t>
   </si>
   <si>
     <t>http://terminology.hl7.org/ValueSet/v3-ConfidentialityClassification</t>
@@ -6638,7 +6641,7 @@
         <v>372</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>360</v>
+        <v>373</v>
       </c>
       <c r="N38" t="s" s="2">
         <v>361</v>
@@ -6673,7 +6676,7 @@
       </c>
       <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>80</v>
@@ -6729,13 +6732,13 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>358</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>80</v>
@@ -6760,7 +6763,7 @@
         <v>242</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M39" t="s" s="2">
         <v>360</v>
@@ -6798,7 +6801,7 @@
       </c>
       <c r="Y39" s="2"/>
       <c r="Z39" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>80</v>
@@ -6854,10 +6857,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6883,10 +6886,10 @@
         <v>316</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6937,7 +6940,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>93</v>
@@ -6955,10 +6958,10 @@
         <v>80</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>80</v>
@@ -6975,10 +6978,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7096,10 +7099,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7219,10 +7222,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7344,10 +7347,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7370,13 +7373,13 @@
         <v>94</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7427,7 +7430,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>93</v>
@@ -7445,30 +7448,30 @@
         <v>80</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7586,10 +7589,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7709,10 +7712,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7738,14 +7741,14 @@
         <v>169</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>80</v>
@@ -7758,7 +7761,7 @@
         <v>80</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="U47" t="s" s="2">
         <v>80</v>
@@ -7773,10 +7776,10 @@
         <v>224</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>80</v>
@@ -7794,7 +7797,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7815,7 +7818,7 @@
         <v>80</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>80</v>
@@ -7824,7 +7827,7 @@
         <v>80</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>80</v>
@@ -7832,10 +7835,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7861,14 +7864,14 @@
         <v>169</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>80</v>
@@ -7881,7 +7884,7 @@
         <v>80</v>
       </c>
       <c r="T48" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="U48" t="s" s="2">
         <v>80</v>
@@ -7917,7 +7920,7 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7938,7 +7941,7 @@
         <v>80</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>80</v>
@@ -7955,10 +7958,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7981,19 +7984,19 @@
         <v>80</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>80</v>
@@ -8042,7 +8045,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8063,7 +8066,7 @@
         <v>80</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>80</v>
@@ -8072,7 +8075,7 @@
         <v>80</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>80</v>
@@ -8080,10 +8083,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8106,19 +8109,19 @@
         <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>80</v>
@@ -8131,7 +8134,7 @@
         <v>80</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="U50" t="s" s="2">
         <v>80</v>
@@ -8167,7 +8170,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8188,7 +8191,7 @@
         <v>80</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>80</v>
@@ -8197,7 +8200,7 @@
         <v>80</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>80</v>
@@ -8205,10 +8208,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8231,19 +8234,19 @@
         <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>80</v>
@@ -8292,7 +8295,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8313,7 +8316,7 @@
         <v>80</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>80</v>
@@ -8330,10 +8333,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8356,19 +8359,19 @@
         <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>80</v>
@@ -8417,7 +8420,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8438,7 +8441,7 @@
         <v>80</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>80</v>
@@ -8455,10 +8458,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8484,14 +8487,14 @@
         <v>107</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>80</v>
@@ -8504,7 +8507,7 @@
         <v>80</v>
       </c>
       <c r="T53" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U53" t="s" s="2">
         <v>80</v>
@@ -8540,7 +8543,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8561,7 +8564,7 @@
         <v>80</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>80</v>
@@ -8578,10 +8581,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8604,17 +8607,17 @@
         <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>80</v>
@@ -8663,7 +8666,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8684,7 +8687,7 @@
         <v>80</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>80</v>
@@ -8701,10 +8704,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8730,13 +8733,13 @@
         <v>147</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8766,7 +8769,7 @@
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>80</v>
@@ -8784,7 +8787,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8796,19 +8799,19 @@
         <v>80</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>80</v>
@@ -8817,15 +8820,15 @@
         <v>80</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8851,13 +8854,13 @@
         <v>316</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8907,7 +8910,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8928,7 +8931,7 @@
         <v>80</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>80</v>
@@ -8945,10 +8948,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9066,10 +9069,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9189,10 +9192,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9314,10 +9317,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9340,13 +9343,13 @@
         <v>80</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9397,7 +9400,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9412,19 +9415,19 @@
         <v>105</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>80</v>
@@ -9435,10 +9438,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9464,13 +9467,13 @@
         <v>242</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9499,10 +9502,10 @@
         <v>159</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>80</v>
@@ -9520,7 +9523,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9532,16 +9535,16 @@
         <v>80</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>80</v>
@@ -9553,15 +9556,15 @@
         <v>80</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9584,13 +9587,13 @@
         <v>94</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9641,7 +9644,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9659,13 +9662,13 @@
         <v>80</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>80</v>
@@ -9674,15 +9677,15 @@
         <v>80</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9708,10 +9711,10 @@
         <v>242</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9742,7 +9745,7 @@
       </c>
       <c r="Y63" s="2"/>
       <c r="Z63" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>80</v>
@@ -9760,7 +9763,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9772,19 +9775,19 @@
         <v>80</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>80</v>
@@ -9793,15 +9796,15 @@
         <v>80</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9827,16 +9830,16 @@
         <v>242</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>80</v>
@@ -9865,7 +9868,7 @@
       </c>
       <c r="Y64" s="2"/>
       <c r="Z64" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>80</v>
@@ -9883,7 +9886,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9895,20 +9898,20 @@
         <v>80</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AM64" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="AN64" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="AN64" t="s" s="2">
-        <v>508</v>
-      </c>
       <c r="AO64" t="s" s="2">
         <v>80</v>
       </c>
@@ -9916,15 +9919,15 @@
         <v>80</v>
       </c>
       <c r="AQ64" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9950,10 +9953,10 @@
         <v>267</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10004,7 +10007,7 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10037,15 +10040,15 @@
         <v>80</v>
       </c>
       <c r="AQ65" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10068,16 +10071,16 @@
         <v>80</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10127,7 +10130,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10145,13 +10148,13 @@
         <v>80</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>80</v>
@@ -10160,7 +10163,7 @@
         <v>80</v>
       </c>
       <c r="AQ66" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
   </sheetData>

--- a/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-simplified-publish.xlsx
+++ b/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-simplified-publish.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2607" uniqueCount="533">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2607" uniqueCount="532">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:54:33+00:00</t>
+    <t>2026-08-06T13:55:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1186,10 +1186,7 @@
     <t>confidentiality</t>
   </si>
   <si>
-    <t>Niveau de confidentialité standard du document (Normal, Restreint, Très restreint).</t>
-  </si>
-  <si>
-    <t>En l'absence d'information de confidentialité disponible, la valeur par défaut à utiliser est N (Normal), conformément à ce qui est déjà pratiqué aujourd'hui pour les documents CDA.</t>
+    <t>Niveau de confidentialité standard du document (Normal, Restreint, Très restreint, ...). En l'absence d'information de confidentialité disponible, la valeur par défaut à utiliser est N (Normal), conformément à ce qui est déjà pratiqué aujourd'hui pour les documents CDA.</t>
   </si>
   <si>
     <t>http://terminology.hl7.org/ValueSet/v3-ConfidentialityClassification</t>
@@ -6641,7 +6638,7 @@
         <v>372</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>373</v>
+        <v>360</v>
       </c>
       <c r="N38" t="s" s="2">
         <v>361</v>
@@ -6676,7 +6673,7 @@
       </c>
       <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>80</v>
@@ -6732,13 +6729,13 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>358</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>80</v>
@@ -6763,7 +6760,7 @@
         <v>242</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M39" t="s" s="2">
         <v>360</v>
@@ -6801,7 +6798,7 @@
       </c>
       <c r="Y39" s="2"/>
       <c r="Z39" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>80</v>
@@ -6857,10 +6854,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6886,10 +6883,10 @@
         <v>316</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6940,7 +6937,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>93</v>
@@ -6958,10 +6955,10 @@
         <v>80</v>
       </c>
       <c r="AL40" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AM40" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>80</v>
@@ -6978,10 +6975,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7099,10 +7096,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7222,10 +7219,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7347,10 +7344,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7373,13 +7370,13 @@
         <v>94</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7430,7 +7427,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>93</v>
@@ -7448,30 +7445,30 @@
         <v>80</v>
       </c>
       <c r="AL44" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="AM44" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="AN44" t="s" s="2">
+      <c r="AO44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP44" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="AO44" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP44" t="s" s="2">
+      <c r="AQ44" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="AQ44" t="s" s="2">
-        <v>394</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7589,10 +7586,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7712,10 +7709,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7741,14 +7738,14 @@
         <v>169</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>80</v>
@@ -7761,7 +7758,7 @@
         <v>80</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="U47" t="s" s="2">
         <v>80</v>
@@ -7776,28 +7773,28 @@
         <v>224</v>
       </c>
       <c r="Y47" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="Z47" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="Z47" t="s" s="2">
+      <c r="AA47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF47" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="AA47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF47" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7818,16 +7815,16 @@
         <v>80</v>
       </c>
       <c r="AM47" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP47" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP47" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>80</v>
@@ -7835,10 +7832,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7864,14 +7861,14 @@
         <v>169</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>80</v>
@@ -7884,7 +7881,7 @@
         <v>80</v>
       </c>
       <c r="T48" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="U48" t="s" s="2">
         <v>80</v>
@@ -7920,7 +7917,7 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7941,7 +7938,7 @@
         <v>80</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>80</v>
@@ -7958,10 +7955,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7984,19 +7981,19 @@
         <v>80</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="N49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>80</v>
@@ -8045,7 +8042,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8066,16 +8063,16 @@
         <v>80</v>
       </c>
       <c r="AM49" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP49" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP49" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>80</v>
@@ -8083,10 +8080,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8109,19 +8106,19 @@
         <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="N50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>80</v>
@@ -8134,43 +8131,43 @@
         <v>80</v>
       </c>
       <c r="T50" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF50" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="U50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8191,16 +8188,16 @@
         <v>80</v>
       </c>
       <c r="AM50" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP50" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP50" t="s" s="2">
-        <v>432</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>80</v>
@@ -8208,10 +8205,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8234,19 +8231,19 @@
         <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="N51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>80</v>
@@ -8295,7 +8292,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8316,7 +8313,7 @@
         <v>80</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>80</v>
@@ -8333,10 +8330,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8359,19 +8356,19 @@
         <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="N52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>80</v>
@@ -8420,7 +8417,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8441,7 +8438,7 @@
         <v>80</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>80</v>
@@ -8458,10 +8455,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8487,14 +8484,14 @@
         <v>107</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>80</v>
@@ -8507,43 +8504,43 @@
         <v>80</v>
       </c>
       <c r="T53" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF53" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="U53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8564,7 +8561,7 @@
         <v>80</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>80</v>
@@ -8581,10 +8578,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8607,17 +8604,17 @@
         <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>80</v>
@@ -8666,7 +8663,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8687,7 +8684,7 @@
         <v>80</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>80</v>
@@ -8704,10 +8701,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8733,13 +8730,13 @@
         <v>147</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8769,7 +8766,7 @@
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>80</v>
@@ -8787,7 +8784,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8799,36 +8796,36 @@
         <v>80</v>
       </c>
       <c r="AJ55" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL55" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="AK55" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL55" t="s" s="2">
+      <c r="AM55" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AN55" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="AM55" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="AN55" t="s" s="2">
+      <c r="AO55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ55" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP55" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ55" t="s" s="2">
-        <v>469</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8854,13 +8851,13 @@
         <v>316</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8910,7 +8907,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8931,7 +8928,7 @@
         <v>80</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>80</v>
@@ -8948,10 +8945,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9069,10 +9066,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9192,10 +9189,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9317,10 +9314,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9343,13 +9340,13 @@
         <v>80</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>481</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9400,7 +9397,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9415,19 +9412,19 @@
         <v>105</v>
       </c>
       <c r="AK60" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AL60" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="AL60" t="s" s="2">
+      <c r="AM60" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="AM60" t="s" s="2">
+      <c r="AN60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO60" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>485</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>80</v>
@@ -9438,10 +9435,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9467,13 +9464,13 @@
         <v>242</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>489</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9502,11 +9499,11 @@
         <v>159</v>
       </c>
       <c r="Y61" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="Z61" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="Z61" t="s" s="2">
-        <v>491</v>
-      </c>
       <c r="AA61" t="s" s="2">
         <v>80</v>
       </c>
@@ -9523,7 +9520,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9535,36 +9532,36 @@
         <v>80</v>
       </c>
       <c r="AJ61" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL61" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="AK61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL61" t="s" s="2">
+      <c r="AM61" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="AM61" t="s" s="2">
+      <c r="AN61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ61" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ61" t="s" s="2">
-        <v>495</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9587,13 +9584,13 @@
         <v>94</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>499</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9644,7 +9641,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9662,30 +9659,30 @@
         <v>80</v>
       </c>
       <c r="AL62" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AM62" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="AM62" t="s" s="2">
+      <c r="AN62" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="AN62" t="s" s="2">
+      <c r="AO62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ62" t="s" s="2">
         <v>502</v>
-      </c>
-      <c r="AO62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ62" t="s" s="2">
-        <v>503</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9711,10 +9708,10 @@
         <v>242</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>505</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>506</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9745,7 +9742,7 @@
       </c>
       <c r="Y63" s="2"/>
       <c r="Z63" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>80</v>
@@ -9763,7 +9760,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9775,36 +9772,36 @@
         <v>80</v>
       </c>
       <c r="AJ63" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL63" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="AK63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL63" t="s" s="2">
+      <c r="AM63" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="AM63" t="s" s="2">
+      <c r="AN63" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="AN63" t="s" s="2">
+      <c r="AO63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ63" t="s" s="2">
         <v>511</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ63" t="s" s="2">
-        <v>512</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9830,16 +9827,16 @@
         <v>242</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>514</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="N64" t="s" s="2">
+      <c r="O64" t="s" s="2">
         <v>516</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>517</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>80</v>
@@ -9868,7 +9865,7 @@
       </c>
       <c r="Y64" s="2"/>
       <c r="Z64" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>80</v>
@@ -9886,7 +9883,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9898,19 +9895,19 @@
         <v>80</v>
       </c>
       <c r="AJ64" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL64" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="AK64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL64" t="s" s="2">
+      <c r="AM64" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="AM64" t="s" s="2">
-        <v>510</v>
-      </c>
       <c r="AN64" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>80</v>
@@ -9919,15 +9916,15 @@
         <v>80</v>
       </c>
       <c r="AQ64" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9953,10 +9950,10 @@
         <v>267</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>521</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>522</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10007,7 +10004,7 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10040,15 +10037,15 @@
         <v>80</v>
       </c>
       <c r="AQ65" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10071,16 +10068,16 @@
         <v>80</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="L66" t="s" s="2">
         <v>525</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="M66" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10130,7 +10127,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10148,22 +10145,22 @@
         <v>80</v>
       </c>
       <c r="AL66" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="AM66" t="s" s="2">
         <v>529</v>
       </c>
-      <c r="AM66" t="s" s="2">
+      <c r="AN66" t="s" s="2">
         <v>530</v>
       </c>
-      <c r="AN66" t="s" s="2">
+      <c r="AO66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ66" t="s" s="2">
         <v>531</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ66" t="s" s="2">
-        <v>532</v>
       </c>
     </row>
   </sheetData>

--- a/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-simplified-publish.xlsx
+++ b/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-simplified-publish.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:55:54+00:00</t>
+    <t>2026-08-06T14:05:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-simplified-publish.xlsx
+++ b/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-simplified-publish.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T14:05:46+00:00</t>
+    <t>2026-08-06T14:06:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1198,7 +1198,7 @@
     <t>visibilityStatus</t>
   </si>
   <si>
-    <t>Statut de visibilité complémentaire du document (motifs de masquage patient, représentants légaux, professionnels).</t>
+    <t>Statut de visibilité du document (invisible patient, invisible représentants légaux, masqué PS, etc...).</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J110-StatutVisibiliteDocument-CISIS/FHIR/JDV-J110-StatutVisibiliteDocument-CISIS</t>

--- a/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-simplified-publish.xlsx
+++ b/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-simplified-publish.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T14:06:47+00:00</t>
+    <t>2026-08-06T14:07:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1162,7 +1162,7 @@
 </t>
   </si>
   <si>
-    <t>Slice sur securityLabel pour distinguer le niveau de confidentialité (NRV) du statut de visibilité complémentaire (TRE A07) : chaque slice est discriminée par son required binding sur un ValueSet fermé (v3-ConfidentialityClassification pour confidentiality, JDV_J110-StatutVisibiliteDocument-CISIS pour visibilityStatus)</t>
+    <t>Slice sur securityLabel pour distinguer le niveau de confidentialité (U, L, M, N, R, V) du statut de visibilité (MASQUE_PS, INVISIBLE_PATIENT, etc...) : chaque slice est discriminée par son required binding sur un ValueSet fermé (v3-ConfidentialityClassification pour confidentiality, JDV_J110-StatutVisibiliteDocument-CISIS pour visibilityStatus)</t>
   </si>
   <si>
     <t>Composition.confidentiality, Composition.meta.security</t>
@@ -2037,7 +2037,7 @@
     <col min="26" max="26" width="102.93359375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="249.46875" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="255.0" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="37.78125" customWidth="true" bestFit="true" hidden="true"/>
